--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:56:12+00:00</t>
+    <t>2026-03-06T09:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -327,14 +327,24 @@
     <t>Adresse de télécommunication du professionnel dans le cadre de l'offre décrite.</t>
   </si>
   <si>
-    <t>SituationOperationnelle.exerciceProfessionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel)
+    <t>SituationOperationnelle.ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel
 </t>
   </si>
   <si>
-    <t>Lien vers la classe ExerciceProfessionnel.</t>
+    <t>Lien vers la classe ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t>SituationOperationnelle.OffreOperationnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/OffreOperationnelle
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe OffreOperationnelle</t>
   </si>
 </sst>
 </file>
@@ -636,7 +646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.703125" customWidth="true" bestFit="true"/>
@@ -649,7 +659,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1780,6 +1790,106 @@
         <v>71</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T09:16:42+00:00</t>
+    <t>2026-04-20T07:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:14:21+00:00</t>
+    <t>2026-04-20T13:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:39:43+00:00</t>
+    <t>2026-04-20T13:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:49:18+00:00</t>
+    <t>2026-04-20T13:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:52:11+00:00</t>
+    <t>2026-04-20T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:01:02+00:00</t>
+    <t>2026-04-20T14:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:11:31+00:00</t>
+    <t>2026-04-20T14:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-SituationOperationnelle.xlsx
+++ b/main/ig/StructureDefinition-SituationOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:36:06+00:00</t>
+    <t>2026-04-20T14:56:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
